--- a/frontend/public/downloads/PMC-v2-Asked-vs-Delivered.xlsx
+++ b/frontend/public/downloads/PMC-v2-Asked-vs-Delivered.xlsx
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-11T15:00:44.087302+00:00</t>
+          <t>2026-08-12T02:16:10.892168+00:00</t>
         </is>
       </c>
     </row>
